--- a/Sajjad data/by_country_and_state/USA/NY.xlsx
+++ b/Sajjad data/by_country_and_state/USA/NY.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1885" uniqueCount="856">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1950" uniqueCount="884">
   <si>
     <t>Business Name</t>
   </si>
@@ -2579,6 +2579,90 @@
   </si>
   <si>
     <t>2026-10-24T01:13:05.262Z</t>
+  </si>
+  <si>
+    <t>O'Keefe Margaret E DDS</t>
+  </si>
+  <si>
+    <t>(716) 284-8477</t>
+  </si>
+  <si>
+    <t>552 3rd St #1, Niagara Falls, NY 14301</t>
+  </si>
+  <si>
+    <t>Niagara Falls</t>
+  </si>
+  <si>
+    <t>CA</t>
+  </si>
+  <si>
+    <t>MondayClosed</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/O%27Keefe+Margaret+E+DDS/data=!4m7!3m6!1s0x89d342e0c497b6e9:0x7de711cf271b5ce!8m2!3d43.0920605!4d-79.0598643!16s%2Fg%2F1w15_f3q!19sChIJ6baXxOBC04kRzrVx8hxx3gc?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T18:45:41.042Z</t>
+  </si>
+  <si>
+    <t>Dr. Mario J. Violante Jr, DDS</t>
+  </si>
+  <si>
+    <t>(716) 297-6453</t>
+  </si>
+  <si>
+    <t>1 Colomba Dr #6, Niagara Falls, NY 14305</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Mario+J.+Violante+Jr,+DDS/data=!4m7!3m6!1s0x89d3678afda34fab:0x56cc121ee4b54296!8m2!3d43.1290953!4d-79.0169594!16s%2Fg%2F1td66974!19sChIJq0-j_Ypn04kRlkK15B4SzFY?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T18:46:09.260Z</t>
+  </si>
+  <si>
+    <t>Dr Bob's Dental Care</t>
+  </si>
+  <si>
+    <t>(716) 657-2550</t>
+  </si>
+  <si>
+    <t>8875 Porter Rd, Niagara Falls, NY 14304</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr+Bob%27s+Dental+Care/data=!4m7!3m6!1s0x89d36882cd52e457:0xd7c0609631df9285!8m2!3d43.1017789!4d-78.9624766!16s%2Fg%2F1thhlhh8!19sChIJV-RSzYJo04kRhZLfMZZgwNc?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T18:46:12.322Z</t>
+  </si>
+  <si>
+    <t>Wanamaker Carrie A DDS</t>
+  </si>
+  <si>
+    <t>(716) 282-5725</t>
+  </si>
+  <si>
+    <t>521 Buffalo Ave, Niagara Falls, NY 14303</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Wanamaker+Carrie+A+DDS/data=!4m7!3m6!1s0x89d342faef522789:0x1bfc089e88f7544c!8m2!3d43.0821549!4d-79.0553284!16s%2Fg%2F125__fwb8!19sChIJiSdS7_pC04kRTFT3iJ4I_Bs?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T18:46:32.028Z</t>
+  </si>
+  <si>
+    <t>Hess Michael D DDS</t>
+  </si>
+  <si>
+    <t>(716) 402-4543</t>
+  </si>
+  <si>
+    <t>1705 Pine Ave Apt 2, Niagara Falls, NY 14301</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Hess+Michael+D+DDS/data=!4m7!3m6!1s0x89d342bf65559be7:0x56e46c61abc4ee4b!8m2!3d43.0949866!4d-79.0411582!16s%2Fg%2F1tql5rx3!19sChIJ55tVZb9C04kRS-7Eq2Fs5FY?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T18:47:09.757Z</t>
   </si>
 </sst>
 </file>
@@ -2959,7 +3043,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M145"/>
+  <dimension ref="A1:M150"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -8921,6 +9005,211 @@
         <v>855</v>
       </c>
     </row>
+    <row r="146" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>856</v>
+      </c>
+      <c r="B146" t="s">
+        <v>857</v>
+      </c>
+      <c r="C146" t="s">
+        <v>28</v>
+      </c>
+      <c r="D146" t="s">
+        <v>858</v>
+      </c>
+      <c r="E146" t="s">
+        <v>859</v>
+      </c>
+      <c r="F146" t="s">
+        <v>18</v>
+      </c>
+      <c r="G146" t="s">
+        <v>860</v>
+      </c>
+      <c r="H146" t="s">
+        <v>128</v>
+      </c>
+      <c r="I146" t="s">
+        <v>21</v>
+      </c>
+      <c r="J146" t="s">
+        <v>861</v>
+      </c>
+      <c r="K146" t="s">
+        <v>23</v>
+      </c>
+      <c r="L146" t="s">
+        <v>862</v>
+      </c>
+      <c r="M146" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="147" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>864</v>
+      </c>
+      <c r="B147" t="s">
+        <v>865</v>
+      </c>
+      <c r="C147" t="s">
+        <v>28</v>
+      </c>
+      <c r="D147" t="s">
+        <v>866</v>
+      </c>
+      <c r="E147" t="s">
+        <v>859</v>
+      </c>
+      <c r="F147" t="s">
+        <v>18</v>
+      </c>
+      <c r="G147" t="s">
+        <v>860</v>
+      </c>
+      <c r="H147" t="s">
+        <v>264</v>
+      </c>
+      <c r="I147" t="s">
+        <v>21</v>
+      </c>
+      <c r="J147" t="s">
+        <v>36</v>
+      </c>
+      <c r="K147" t="s">
+        <v>23</v>
+      </c>
+      <c r="L147" t="s">
+        <v>867</v>
+      </c>
+      <c r="M147" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="148" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>869</v>
+      </c>
+      <c r="B148" t="s">
+        <v>870</v>
+      </c>
+      <c r="C148" t="s">
+        <v>28</v>
+      </c>
+      <c r="D148" t="s">
+        <v>871</v>
+      </c>
+      <c r="E148" t="s">
+        <v>859</v>
+      </c>
+      <c r="F148" t="s">
+        <v>18</v>
+      </c>
+      <c r="G148" t="s">
+        <v>860</v>
+      </c>
+      <c r="H148" t="s">
+        <v>121</v>
+      </c>
+      <c r="I148" t="s">
+        <v>21</v>
+      </c>
+      <c r="J148" t="s">
+        <v>36</v>
+      </c>
+      <c r="K148" t="s">
+        <v>23</v>
+      </c>
+      <c r="L148" t="s">
+        <v>872</v>
+      </c>
+      <c r="M148" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="149" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>874</v>
+      </c>
+      <c r="B149" t="s">
+        <v>875</v>
+      </c>
+      <c r="C149" t="s">
+        <v>55</v>
+      </c>
+      <c r="D149" t="s">
+        <v>876</v>
+      </c>
+      <c r="E149" t="s">
+        <v>859</v>
+      </c>
+      <c r="F149" t="s">
+        <v>18</v>
+      </c>
+      <c r="G149" t="s">
+        <v>860</v>
+      </c>
+      <c r="H149" t="s">
+        <v>36</v>
+      </c>
+      <c r="I149" t="s">
+        <v>37</v>
+      </c>
+      <c r="J149" t="s">
+        <v>36</v>
+      </c>
+      <c r="K149" t="s">
+        <v>23</v>
+      </c>
+      <c r="L149" t="s">
+        <v>877</v>
+      </c>
+      <c r="M149" t="s">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="150" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>879</v>
+      </c>
+      <c r="B150" t="s">
+        <v>880</v>
+      </c>
+      <c r="C150" t="s">
+        <v>28</v>
+      </c>
+      <c r="D150" t="s">
+        <v>881</v>
+      </c>
+      <c r="E150" t="s">
+        <v>859</v>
+      </c>
+      <c r="F150" t="s">
+        <v>18</v>
+      </c>
+      <c r="G150" t="s">
+        <v>860</v>
+      </c>
+      <c r="H150" t="s">
+        <v>276</v>
+      </c>
+      <c r="I150" t="s">
+        <v>21</v>
+      </c>
+      <c r="J150" t="s">
+        <v>36</v>
+      </c>
+      <c r="K150" t="s">
+        <v>23</v>
+      </c>
+      <c r="L150" t="s">
+        <v>882</v>
+      </c>
+      <c r="M150" t="s">
+        <v>883</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
